--- a/data/go_japan.xlsx
+++ b/data/go_japan.xlsx
@@ -1085,7 +1085,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trip.com App Homepage Banner</t>
+          <t>App Homepage Banner</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
